--- a/qa/user_stories.xlsx
+++ b/qa/user_stories.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,9 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
@@ -82,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -98,6 +101,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1830,6 +1837,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1848,6 +1856,530 @@
       </c>
       <c r="F34" s="6" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>US-31</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Mobile layout</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>As a phone user, I reach real data without a long scroll</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Load / at 375x812, measure first board row</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Board content reachable in the first screen or just below</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>First row at y=1063 on an 812px screen: controls block 236px tall, board explanation 10 lines, search and toggle each a full row</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Scoring+Defense share a row, explanations clamp to 3 lines behind 'What this shows', search+toggle share a row; first row y=833</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>US-32</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>As a reader, the weekly chart uses its plot area</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Screenshot trend chart at 375 and 1280</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Series fill the plot; differences legible</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>y-axis hard-floored at 0.8 while the highest weekly score in 13 seasons is 0.574, so a quarter of the plot was always empty</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Ceiling 0.6 — still fixed so seasons stay comparable, still pinned at 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>US-33</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>As a phone user, the scatter keeps a readable aspect ratio</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Screenshot calibration scatter at 375</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Near-square so the diagonal is meaningful</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>351x333 (1.05:1); axis labels and quadrant notes legible; dots r=4</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>US-34</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>As a reader, the cross-season table is legible on a phone</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Screenshot career table at 375</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>One line per source; interval plot readable</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Monogram chip and full name rendered side by side in a 124px wrapped cell: 54px rows and the interval plot squeezed to 62px</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Chip hidden on narrow; rows 34px, plot 86px</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>US-35</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>As a reader, the interval plot's zero line is unmistakable</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Inspect .fp at 375 and 1280</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Zero rule clearly visible — an interval touching it is the finding</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>1px hairline in --baseline, the faintest token; lost against the row</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Uses --muted and overhangs the row</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>US-36</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Drill-in</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, the player history panel shows which season each row is</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Click a board row at 375</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Season column present against every row</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Season column hidden: the mobile rule hiding the board's rank number was unscoped and also matched rows of the nested history table</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Rule scoped to the board's own thead/tbody rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>US-37</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>As a reader, footnotes read as sentences</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Screenshot leaderboard footnote at 375</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Inline link flows within the sentence</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>'Across all seasons' collapsed into a 3-line column mid-sentence: .chart-note was display:flex so the anchor became a flex item at min-content width</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>display:block</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>US-38</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Empty states</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>As a reader, controls that do nothing are not shown</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Load a format with no board; IDP lens; no-match search</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>No dead controls</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Source-column toggle rendered as a blank 351x40 button — every early return in renderBoard skipped the code that labels it</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>setSrcToggle() on every path; hidden unless a table was drawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>US-39</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Scrolling</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, the board header and player column stay pinned</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Scroll board vertically and horizontally at 375</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>thead and .pcol remain visible</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Sticky verified visually under internal scroll and by geometry at max scrollLeft</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>US-40</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Scrolling</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>As a phone user, no section scrolls the page sideways</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Measure every scroll container at 375, 3 seasons x 3 formats</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Page never overflows; wide tables scroll inside their own box</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Only the 13-season matrix scrolls internally, with a sticky source column</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>US-41</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>As a user rotating my phone, the layout follows</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Cross the 640 and 820 breakpoints</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Columns, headings and charts re-resolve</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Board columns re-resolve against the live viewport; explicit toggle still wins; charts redraw on resize, orientationchange and a staged post-layout check</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Pass on first test</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Failed and fixed</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Total stories</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>All retests passing</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/qa/user_stories.xlsx
+++ b/qa/user_stories.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2339,44 +2339,877 @@
       </c>
       <c r="H45" s="7" t="inlineStr"/>
     </row>
-    <row r="46"/>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>US-42</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, I can mark a player as drafted by me</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Tick ME on 6 players across positions</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Row tints as mine; roster count rises; slot filled</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>6/15 after six picks; QB/RB1/RB2/WR1/FLEX/K filled</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>US-43</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, I can mark a player as drafted by someone else</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Tick OUT on 2 players</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Row greys out and strikes through; roster count unchanged</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>is-them class applied; count stayed 6/15; chip read '8 off the board'</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>US-44</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, the two checkboxes cannot disagree</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Tick ME then OUT on the same row</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>ME unticks; stored state is 'them'</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>me=false, them=true, stored 'them'</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>US-45</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, I can undo a misclick on the clock</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Untick the ticked box</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Row returns to the board; count drops; key removed from storage</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>class cleared, 6/15 -&gt; 5/15, key gone</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>US-46</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, ticking a box does not open the season drill-in</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Click the ME label on a row</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Checkbox toggles; no detail row inserted</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>0 detail rows after the click; row click still opens one</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>US-47</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, a pick does not lose my place on the board</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Scroll board to 900px, tick a box</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Scroll position and tbody identity preserved</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>scrollTop still 900; same tbody node repainted in place</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>US-48</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, I can thin the board to players still available</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Toggle Hide drafted with 8 gone</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Row count drops by exactly the number drafted, and restores</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>431 -&gt; 423 -&gt; 431</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>US-49</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Roster</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, my third RB lands in FLEX rather than a second RB slot</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Draft 3 RBs, 1 WR, 1 QB, 1 K</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>RB1, RB2 filled, third RB in FLEX; bench empty</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>McCaffrey in FLEX behind Gibbs and Robinson</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>US-50</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Roster</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, I can see which starting spots are still open</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Read the Still need block after six picks</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Pills for each unfilled slot with counts</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>WR, TE, DST shown; '3 starting spots left to fill'</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>US-51</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Roster</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, I am shown the best player available at a position I need</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Read Best available with WR/TE/DST open</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Top undrafted players filtered to needed positions, consensus order</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Nacua 3.8, Smith-Njigba 6, St. Brown 7.5</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>US-52</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Roster</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, the lineup comes from my league, not a hardcoded one</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Read slot labels against predraft.json league block</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>QB RB1 RB2 WR1 WR2 TE FLEX DST K, bench 6</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>matches scripts/league.py via predraft.json; total 15</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>US-53</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, my picks survive a reload mid-draft</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Reload with 8 recorded</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Rows, checkboxes, roster and count all restored</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>6 me / 2 them / 8 checked / 6-of-15 after reload</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>US-54</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, switching scoring format keeps my picks</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Switch half-PPR -&gt; PPR -&gt; All -&gt; half-PPR</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Roster and marks unchanged in every format</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>6/15 and 6 marked rows throughout</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>US-55</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>As a user, last year's draft does not appear on this year's board</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Record picks on 2026, switch to 2024 and back</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>2024 board is clean; 2026 restored on return</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>2024 read 0/15; 2026 back to 6/15</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>US-56</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, I can clear the board and start over</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Reset with 10 recorded</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Confirms, then clears marks, storage, chip and roster</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Reset (10) -&gt; Reset (0), 0/15, storage '{}', chip removed</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>US-57</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Scrolling</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>As a phone user, the new pick column does not crowd out the data</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Measure the three sticky columns at 375</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Columns tile with no overlap and leave usable width</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>First cut took 316 of 375px. Shrank header labels, let the name wrap: 222px, 136px of data room, gaps 0</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>I-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>US-58</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Scrolling</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>As a user, the pinned columns line up once the board scrolls sideways</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Scroll board horizontally at 375 and 1280</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Each sticky left offset equals the real width before it</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>CSS-declared widths were 5px under what was laid out. Now measured after render and fed back</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>I-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>US-59</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>As a user rotating my phone, the pinned columns resize with it</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Fire resize after crossing the 720 breakpoint</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Offsets re-measure to the narrow widths</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Inline vars outranked the media query, so columns stayed at desktop width. Vars now cleared before measuring: 68/63 -&gt; 50/40</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>I-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>US-60</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>As a phone user, the roster panel does not bury the board</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Load at 375 with no stored preference</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Panel opens collapsed as a 38px bar carrying the count; expands on tap and fits</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>collapsed 38px; expanded 347px at top 457 of 812</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>Pass on first test</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="B69" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>Failed and fixed</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="B70" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>Total stories</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="B71" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>All retests passing</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -2393,7 +3226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2809,6 +3642,80 @@
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>I-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Three sticky columns took 316px of a 375px screen, leaving no room for any data</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Draft board, phone</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Shrink the pick/rank header labels, let the player name wrap, tighten cell padding (222px, 136px of data room)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>I-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Sticky column offsets were CSS constants, but a table cell's width is a minimum the browser may exceed — the pick column laid out 5px wider than declared, so the columns overlapped once the board scrolled sideways</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Draft board</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Measure the laid-out header widths after each render and feed them back as the offsets; clear the inline values before measuring so the phone media query is not outranked, and re-measure on resize</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>

--- a/qa/user_stories.xlsx
+++ b/qa/user_stories.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Tick ME on 6 players across positions</t>
+          <t>Press + ROSTER on 6 players across positions</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Tick OUT on 2 players</t>
+          <t>Press DRAFTED on 2 players</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Tick ME then OUT on the same row</t>
+          <t>Press + ROSTER then DRAFTED on the same row</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>ME unticks; stored state is 'them'</t>
+          <t>+ ROSTER unpresses; stored state is 'them'</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Untick the ticked box</t>
+          <t>Press the lit pill again</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Click the ME label on a row</t>
+          <t>Click the + ROSTER pill on a row</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Checkbox toggles; no detail row inserted</t>
+          <t>Pill toggles; no detail row inserted</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Toggle Hide drafted with 8 gone</t>
+          <t>Toggle Hide drafted with 8 off the board</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -3152,6 +3152,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="E66" t="inlineStr">
         <is>
@@ -3172,44 +3173,373 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68"/>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>US-61</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, the row controls say what they do rather than showing a tick state</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Read the pick column against three real draft tools</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Labelled buttons, in the words the industry uses</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Shipped as ME/OUT checkbox squares. No tool does that — FantasyPros uses a labelled Draft button and strikes drafted players through. Rebuilt as + ROSTER / DRAFTED pills</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>I-13</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>US-62</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, the roster button tells me whether he is already on my team</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Press + ROSTER and read the label</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Label changes to the done state</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>'+ ROSTER' -&gt; '✓ ROSTER', aria-pressed true, row tints green</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>US-63</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Draft day</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter, pressing the lit pill puts him back on the board</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Press the lit pill a second time</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>State clears, label reverts, count drops</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>'✓ ROSTER' -&gt; '+ ROSTER', 1/15 -&gt; 0/15, storage '{}'</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>US-64</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Scrolling</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>As a phone user, the pick column does not cost the board its width</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Measure the pick column at 375 and 1143</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Comfortably under the two-pill cost</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Side by side the pills took 104px of sticky column. Stacked: 57px desktop, 40px phone</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>I-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>US-65</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Mobile layout</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>As a drafter on a phone, the board is on screen when the page opens</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Measure the board's offset at 375x812</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Board visible without scrolling</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Board started at 830px on an 812px screen — nothing but explanation above it. Intro clamped to two lines, legend folded, controls tightened: 423px, six rows visible</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>I-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>US-66</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Mobile layout</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>As a phone user, I can still read the intro and the legend if I want them</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Tap 'more' and 'How to read the board'</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Both expand and collapse again</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>more -&gt; less (board 423 -&gt; 574px), details toggles; both full-width on desktop</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>US-67</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>As a laptop user, nothing on the page is folded away</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Load at 1143 and read the legend and intro</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Full intro, full legend, no disclosure controls</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>summary and 'more' both display:none above 720px</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>Pass on first test</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="B79" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>Failed and fixed</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="B80" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>Total stories</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="B81" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>All retests passing</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -3226,7 +3556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3714,6 +4044,80 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>I-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Pick controls shipped as two small ME/OUT checkbox squares — the wrong control and the wrong words. Reading them meant working out which of two boxes was ticked, and side by side they took 104px of sticky column</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Draft board</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Two stacked labelled pills, '+ ROSTER' (becomes '✓ ROSTER') and 'DRAFTED', following the labelled-button convention in FantasyPros' draft simulator and cheat sheets. 57px desktop, 40px phone</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>I-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>On a 375x812 phone the board began at 830px — entirely below the fold, behind the intro, the legend and four rows of controls. The draft-day feature was unreachable on the device it was built for</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Draft board, phone</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Clamp the intro to two lines behind a sibling 'more' button (the cue cannot sit inside the clamped box), fold the legend into a details element, tighten the control bar. Board now starts at 423px</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
